--- a/ig/nr-corrections/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/nr-corrections/StructureDefinition-as-dr-practitioner.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22466" uniqueCount="1250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22466" uniqueCount="1251">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:20:08+00:00</t>
+    <t>2024-02-12T14:26:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3025,426 +3025,424 @@
     <t>[Donnée restreinte] : Lieu de formation pour l'obtention du diplôme (lieuFormation).</t>
   </si>
   <si>
-    <t>Practitioner.qualification:profession</t>
+    <t>Practitioner.qualification:exercicePro</t>
+  </si>
+  <si>
+    <t>exercicePro</t>
+  </si>
+  <si>
+    <t>profession : exercice professionnel ou future profession de l'étudiant et la catégorie de profession.</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.modifierExtension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.identifier</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR36.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR47.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR48.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR49.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR50.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR51.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR52.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR53.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR54.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR55.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR56.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR57.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR58.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.system</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.version</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.code</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.display</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:degreeR226.userSelected</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:categorieProfession</t>
+  </si>
+  <si>
+    <t>categorieProfession</t>
+  </si>
+  <si>
+    <t>Catégorie professionnelle indiquant si le professionnel exerce sa profession en tant que Militaire, Civil, Fonctionnaire ou Etudiant (categorieProfessionnelle).</t>
+  </si>
+  <si>
+    <t>https://mos.esante.gouv.fr/NOS/JDV_J89-CategorieProfessionnelle-RASS/FHIR/JDV-J89-CategorieProfessionnelle-RASS</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.code.coding:profession</t>
   </si>
   <si>
     <t>profession</t>
   </si>
   <si>
-    <t>profession : Profession exercée ou future profession de l'étudiant.
-categorieProfessionnelle : Indique si le professionnel exerce sa profession en tant que :
-M: Militaire
-C: Civil
-F: Fonctionnaire
-E: Etudiant</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.modifierExtension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.identifier</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR36.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR47.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR48.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR49.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR50.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR51.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR52.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR53.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR54.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR55.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR56.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR57.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR58.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.system</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.version</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.code</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.display</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:degreeR226.userSelected</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:categorieProfession</t>
-  </si>
-  <si>
-    <t>categorieProfession</t>
-  </si>
-  <si>
-    <t>Catégorie professionnelle indiqant si le professionnel exerce sa profession en tant que Militaire, Civil, Fonctionnaire ou Etudiant (categorieProfessionnelle).</t>
-  </si>
-  <si>
-    <t>https://mos.esante.gouv.fr/NOS/JDV_J89-CategorieProfessionnelle-RASS/FHIR/JDV-J89-CategorieProfessionnelle-RASS</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.code.coding:profession</t>
-  </si>
-  <si>
     <t>Profession exercée : de santé (professionSante) TRE G15, du social (professionSocial) TRE R94, à usage de titre professionnel (usagerTitre) TRE R95, ou autre profession (autreProfession) TRE R291</t>
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/JDV_J106-EnsembleProfession-RASS/FHIR/JDV-J106-EnsembleProfession-RASS</t>
   </si>
   <si>
-    <t>Practitioner.qualification:profession.code.text</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.period</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.period.id</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.period.extension</t>
-  </si>
-  <si>
-    <t>Practitioner.qualification:profession.period.start</t>
+    <t>Practitioner.qualification:exercicePro.code.text</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period.id</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period.extension</t>
+  </si>
+  <si>
+    <t>Practitioner.qualification:exercicePro.period.start</t>
   </si>
   <si>
     <t>[Donnée restreinte] : Date à partir de laquelle le professionnel n’exerce plus cette profession (dateFinEffetExercice).</t>
   </si>
   <si>
-    <t>Practitioner.qualification:profession.period.end</t>
+    <t>Practitioner.qualification:exercicePro.period.end</t>
   </si>
   <si>
     <t>End time with inclusive boundary, if not ongoing</t>
   </si>
   <si>
-    <t>Practitioner.qualification:profession.issuer</t>
+    <t>Practitioner.qualification:exercicePro.issuer</t>
   </si>
   <si>
     <t>Practitioner.qualification:savoirFaire</t>
@@ -36518,7 +36516,7 @@
         <v>74</v>
       </c>
       <c r="G316" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H316" t="s" s="2">
         <v>73</v>
@@ -37342,7 +37340,7 @@
         <v>74</v>
       </c>
       <c r="G324" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H324" t="s" s="2">
         <v>73</v>
@@ -38166,7 +38164,7 @@
         <v>74</v>
       </c>
       <c r="G332" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H332" t="s" s="2">
         <v>73</v>
@@ -38990,7 +38988,7 @@
         <v>74</v>
       </c>
       <c r="G340" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H340" t="s" s="2">
         <v>73</v>
@@ -39814,7 +39812,7 @@
         <v>74</v>
       </c>
       <c r="G348" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H348" t="s" s="2">
         <v>73</v>
@@ -40638,7 +40636,7 @@
         <v>74</v>
       </c>
       <c r="G356" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H356" t="s" s="2">
         <v>73</v>
@@ -41462,7 +41460,7 @@
         <v>74</v>
       </c>
       <c r="G364" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H364" t="s" s="2">
         <v>73</v>
@@ -42286,7 +42284,7 @@
         <v>74</v>
       </c>
       <c r="G372" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H372" t="s" s="2">
         <v>73</v>
@@ -43110,7 +43108,7 @@
         <v>74</v>
       </c>
       <c r="G380" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H380" t="s" s="2">
         <v>73</v>
@@ -43934,7 +43932,7 @@
         <v>74</v>
       </c>
       <c r="G388" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H388" t="s" s="2">
         <v>73</v>
@@ -44758,7 +44756,7 @@
         <v>74</v>
       </c>
       <c r="G396" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H396" t="s" s="2">
         <v>73</v>
@@ -45582,7 +45580,7 @@
         <v>74</v>
       </c>
       <c r="G404" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H404" t="s" s="2">
         <v>73</v>
@@ -46406,7 +46404,7 @@
         <v>74</v>
       </c>
       <c r="G412" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H412" t="s" s="2">
         <v>73</v>
@@ -47230,7 +47228,7 @@
         <v>74</v>
       </c>
       <c r="G420" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H420" t="s" s="2">
         <v>73</v>
@@ -49896,7 +49894,7 @@
         <v>74</v>
       </c>
       <c r="G446" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H446" t="s" s="2">
         <v>73</v>
@@ -50720,7 +50718,7 @@
         <v>74</v>
       </c>
       <c r="G454" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H454" t="s" s="2">
         <v>73</v>
@@ -51544,7 +51542,7 @@
         <v>74</v>
       </c>
       <c r="G462" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H462" t="s" s="2">
         <v>73</v>
@@ -52368,7 +52366,7 @@
         <v>74</v>
       </c>
       <c r="G470" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H470" t="s" s="2">
         <v>73</v>
@@ -53192,7 +53190,7 @@
         <v>74</v>
       </c>
       <c r="G478" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H478" t="s" s="2">
         <v>73</v>
@@ -54016,7 +54014,7 @@
         <v>74</v>
       </c>
       <c r="G486" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H486" t="s" s="2">
         <v>73</v>
@@ -54840,7 +54838,7 @@
         <v>74</v>
       </c>
       <c r="G494" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H494" t="s" s="2">
         <v>73</v>
@@ -55664,7 +55662,7 @@
         <v>74</v>
       </c>
       <c r="G502" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H502" t="s" s="2">
         <v>73</v>
@@ -56488,7 +56486,7 @@
         <v>74</v>
       </c>
       <c r="G510" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H510" t="s" s="2">
         <v>73</v>
@@ -57312,7 +57310,7 @@
         <v>74</v>
       </c>
       <c r="G518" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H518" t="s" s="2">
         <v>73</v>
@@ -58136,7 +58134,7 @@
         <v>74</v>
       </c>
       <c r="G526" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H526" t="s" s="2">
         <v>73</v>
@@ -58960,7 +58958,7 @@
         <v>74</v>
       </c>
       <c r="G534" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H534" t="s" s="2">
         <v>73</v>
@@ -59784,7 +59782,7 @@
         <v>74</v>
       </c>
       <c r="G542" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H542" t="s" s="2">
         <v>73</v>
@@ -60608,7 +60606,7 @@
         <v>74</v>
       </c>
       <c r="G550" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H550" t="s" s="2">
         <v>73</v>
@@ -61526,7 +61524,7 @@
         <v>650</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>973</v>
+        <v>1100</v>
       </c>
       <c r="D559" t="s" s="2">
         <v>73</v>
@@ -61551,7 +61549,7 @@
         <v>140</v>
       </c>
       <c r="L559" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="M559" t="s" s="2">
         <v>335</v>
@@ -61589,7 +61587,7 @@
       </c>
       <c r="Y559" s="2"/>
       <c r="Z559" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="AA559" t="s" s="2">
         <v>73</v>
@@ -61624,7 +61622,7 @@
     </row>
     <row r="560" hidden="true">
       <c r="A560" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="B560" t="s" s="2">
         <v>814</v>
@@ -61728,7 +61726,7 @@
     </row>
     <row r="561" hidden="true">
       <c r="A561" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="B561" t="s" s="2">
         <v>815</v>
@@ -61832,7 +61830,7 @@
     </row>
     <row r="562" hidden="true">
       <c r="A562" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B562" t="s" s="2">
         <v>960</v>
@@ -61932,7 +61930,7 @@
     </row>
     <row r="563" hidden="true">
       <c r="A563" t="s" s="2">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="B563" t="s" s="2">
         <v>962</v>
@@ -62034,7 +62032,7 @@
     </row>
     <row r="564" hidden="true">
       <c r="A564" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="B564" t="s" s="2">
         <v>964</v>
@@ -62063,7 +62061,7 @@
         <v>259</v>
       </c>
       <c r="L564" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="M564" t="s" s="2">
         <v>261</v>
@@ -62136,7 +62134,7 @@
     </row>
     <row r="565" hidden="true">
       <c r="A565" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="B565" t="s" s="2">
         <v>967</v>
@@ -62165,7 +62163,7 @@
         <v>259</v>
       </c>
       <c r="L565" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="M565" t="s" s="2">
         <v>268</v>
@@ -62240,7 +62238,7 @@
     </row>
     <row r="566" hidden="true">
       <c r="A566" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="B566" t="s" s="2">
         <v>819</v>
@@ -62342,13 +62340,13 @@
     </row>
     <row r="567" hidden="true">
       <c r="A567" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="B567" t="s" s="2">
         <v>626</v>
       </c>
       <c r="C567" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D567" t="s" s="2">
         <v>73</v>
@@ -62373,7 +62371,7 @@
         <v>627</v>
       </c>
       <c r="L567" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="M567" t="s" s="2">
         <v>629</v>
@@ -62444,7 +62442,7 @@
     </row>
     <row r="568" hidden="true">
       <c r="A568" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="B568" t="s" s="2">
         <v>631</v>
@@ -62544,7 +62542,7 @@
     </row>
     <row r="569" hidden="true">
       <c r="A569" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="B569" t="s" s="2">
         <v>632</v>
@@ -62646,7 +62644,7 @@
     </row>
     <row r="570" hidden="true">
       <c r="A570" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="B570" t="s" s="2">
         <v>633</v>
@@ -62750,7 +62748,7 @@
     </row>
     <row r="571" hidden="true">
       <c r="A571" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="B571" t="s" s="2">
         <v>638</v>
@@ -62852,7 +62850,7 @@
     </row>
     <row r="572" hidden="true">
       <c r="A572" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="B572" t="s" s="2">
         <v>642</v>
@@ -62954,7 +62952,7 @@
     </row>
     <row r="573" hidden="true">
       <c r="A573" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="B573" t="s" s="2">
         <v>648</v>
@@ -63054,7 +63052,7 @@
     </row>
     <row r="574" hidden="true">
       <c r="A574" t="s" s="2">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="B574" t="s" s="2">
         <v>649</v>
@@ -63156,7 +63154,7 @@
     </row>
     <row r="575" hidden="true">
       <c r="A575" t="s" s="2">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="B575" t="s" s="2">
         <v>650</v>
@@ -63258,7 +63256,7 @@
     </row>
     <row r="576" hidden="true">
       <c r="A576" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="B576" t="s" s="2">
         <v>650</v>
@@ -63274,7 +63272,7 @@
         <v>74</v>
       </c>
       <c r="G576" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H576" t="s" s="2">
         <v>73</v>
@@ -63362,7 +63360,7 @@
     </row>
     <row r="577" hidden="true">
       <c r="A577" t="s" s="2">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="B577" t="s" s="2">
         <v>656</v>
@@ -63462,7 +63460,7 @@
     </row>
     <row r="578" hidden="true">
       <c r="A578" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="B578" t="s" s="2">
         <v>658</v>
@@ -63564,7 +63562,7 @@
     </row>
     <row r="579" hidden="true">
       <c r="A579" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="B579" t="s" s="2">
         <v>660</v>
@@ -63668,7 +63666,7 @@
     </row>
     <row r="580" hidden="true">
       <c r="A580" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="B580" t="s" s="2">
         <v>664</v>
@@ -63770,7 +63768,7 @@
     </row>
     <row r="581" hidden="true">
       <c r="A581" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="B581" t="s" s="2">
         <v>666</v>
@@ -63874,7 +63872,7 @@
     </row>
     <row r="582" hidden="true">
       <c r="A582" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="B582" t="s" s="2">
         <v>668</v>
@@ -63978,7 +63976,7 @@
     </row>
     <row r="583" hidden="true">
       <c r="A583" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="B583" t="s" s="2">
         <v>670</v>
@@ -64082,7 +64080,7 @@
     </row>
     <row r="584" hidden="true">
       <c r="A584" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="B584" t="s" s="2">
         <v>650</v>
@@ -64098,7 +64096,7 @@
         <v>74</v>
       </c>
       <c r="G584" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H584" t="s" s="2">
         <v>73</v>
@@ -64186,7 +64184,7 @@
     </row>
     <row r="585" hidden="true">
       <c r="A585" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="B585" t="s" s="2">
         <v>656</v>
@@ -64286,7 +64284,7 @@
     </row>
     <row r="586" hidden="true">
       <c r="A586" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="B586" t="s" s="2">
         <v>658</v>
@@ -64388,7 +64386,7 @@
     </row>
     <row r="587" hidden="true">
       <c r="A587" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="B587" t="s" s="2">
         <v>660</v>
@@ -64492,7 +64490,7 @@
     </row>
     <row r="588" hidden="true">
       <c r="A588" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="B588" t="s" s="2">
         <v>664</v>
@@ -64594,7 +64592,7 @@
     </row>
     <row r="589" hidden="true">
       <c r="A589" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="B589" t="s" s="2">
         <v>666</v>
@@ -64698,7 +64696,7 @@
     </row>
     <row r="590" hidden="true">
       <c r="A590" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="B590" t="s" s="2">
         <v>668</v>
@@ -64802,7 +64800,7 @@
     </row>
     <row r="591" hidden="true">
       <c r="A591" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="B591" t="s" s="2">
         <v>670</v>
@@ -64906,7 +64904,7 @@
     </row>
     <row r="592" hidden="true">
       <c r="A592" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="B592" t="s" s="2">
         <v>650</v>
@@ -64922,7 +64920,7 @@
         <v>74</v>
       </c>
       <c r="G592" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H592" t="s" s="2">
         <v>73</v>
@@ -65010,7 +65008,7 @@
     </row>
     <row r="593" hidden="true">
       <c r="A593" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="B593" t="s" s="2">
         <v>656</v>
@@ -65110,7 +65108,7 @@
     </row>
     <row r="594" hidden="true">
       <c r="A594" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="B594" t="s" s="2">
         <v>658</v>
@@ -65212,7 +65210,7 @@
     </row>
     <row r="595" hidden="true">
       <c r="A595" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="B595" t="s" s="2">
         <v>660</v>
@@ -65316,7 +65314,7 @@
     </row>
     <row r="596" hidden="true">
       <c r="A596" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="B596" t="s" s="2">
         <v>664</v>
@@ -65418,7 +65416,7 @@
     </row>
     <row r="597" hidden="true">
       <c r="A597" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="B597" t="s" s="2">
         <v>666</v>
@@ -65522,7 +65520,7 @@
     </row>
     <row r="598" hidden="true">
       <c r="A598" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="B598" t="s" s="2">
         <v>668</v>
@@ -65626,7 +65624,7 @@
     </row>
     <row r="599" hidden="true">
       <c r="A599" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="B599" t="s" s="2">
         <v>670</v>
@@ -65730,7 +65728,7 @@
     </row>
     <row r="600" hidden="true">
       <c r="A600" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="B600" t="s" s="2">
         <v>650</v>
@@ -65746,7 +65744,7 @@
         <v>74</v>
       </c>
       <c r="G600" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H600" t="s" s="2">
         <v>73</v>
@@ -65834,7 +65832,7 @@
     </row>
     <row r="601" hidden="true">
       <c r="A601" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="B601" t="s" s="2">
         <v>656</v>
@@ -65934,7 +65932,7 @@
     </row>
     <row r="602" hidden="true">
       <c r="A602" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="B602" t="s" s="2">
         <v>658</v>
@@ -66036,7 +66034,7 @@
     </row>
     <row r="603" hidden="true">
       <c r="A603" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="B603" t="s" s="2">
         <v>660</v>
@@ -66140,7 +66138,7 @@
     </row>
     <row r="604" hidden="true">
       <c r="A604" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B604" t="s" s="2">
         <v>664</v>
@@ -66242,7 +66240,7 @@
     </row>
     <row r="605" hidden="true">
       <c r="A605" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="B605" t="s" s="2">
         <v>666</v>
@@ -66346,7 +66344,7 @@
     </row>
     <row r="606" hidden="true">
       <c r="A606" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="B606" t="s" s="2">
         <v>668</v>
@@ -66450,7 +66448,7 @@
     </row>
     <row r="607" hidden="true">
       <c r="A607" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="B607" t="s" s="2">
         <v>670</v>
@@ -66554,7 +66552,7 @@
     </row>
     <row r="608" hidden="true">
       <c r="A608" t="s" s="2">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="B608" t="s" s="2">
         <v>650</v>
@@ -66570,7 +66568,7 @@
         <v>74</v>
       </c>
       <c r="G608" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H608" t="s" s="2">
         <v>73</v>
@@ -66658,7 +66656,7 @@
     </row>
     <row r="609" hidden="true">
       <c r="A609" t="s" s="2">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="B609" t="s" s="2">
         <v>656</v>
@@ -66758,7 +66756,7 @@
     </row>
     <row r="610" hidden="true">
       <c r="A610" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="B610" t="s" s="2">
         <v>658</v>
@@ -66860,7 +66858,7 @@
     </row>
     <row r="611" hidden="true">
       <c r="A611" t="s" s="2">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="B611" t="s" s="2">
         <v>660</v>
@@ -66964,7 +66962,7 @@
     </row>
     <row r="612" hidden="true">
       <c r="A612" t="s" s="2">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="B612" t="s" s="2">
         <v>664</v>
@@ -67066,7 +67064,7 @@
     </row>
     <row r="613" hidden="true">
       <c r="A613" t="s" s="2">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="B613" t="s" s="2">
         <v>666</v>
@@ -67170,7 +67168,7 @@
     </row>
     <row r="614" hidden="true">
       <c r="A614" t="s" s="2">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="B614" t="s" s="2">
         <v>668</v>
@@ -67274,7 +67272,7 @@
     </row>
     <row r="615" hidden="true">
       <c r="A615" t="s" s="2">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="B615" t="s" s="2">
         <v>670</v>
@@ -67378,7 +67376,7 @@
     </row>
     <row r="616" hidden="true">
       <c r="A616" t="s" s="2">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="B616" t="s" s="2">
         <v>650</v>
@@ -67394,7 +67392,7 @@
         <v>74</v>
       </c>
       <c r="G616" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H616" t="s" s="2">
         <v>73</v>
@@ -67482,7 +67480,7 @@
     </row>
     <row r="617" hidden="true">
       <c r="A617" t="s" s="2">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="B617" t="s" s="2">
         <v>656</v>
@@ -67582,7 +67580,7 @@
     </row>
     <row r="618" hidden="true">
       <c r="A618" t="s" s="2">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="B618" t="s" s="2">
         <v>658</v>
@@ -67684,7 +67682,7 @@
     </row>
     <row r="619" hidden="true">
       <c r="A619" t="s" s="2">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="B619" t="s" s="2">
         <v>660</v>
@@ -67788,7 +67786,7 @@
     </row>
     <row r="620" hidden="true">
       <c r="A620" t="s" s="2">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="B620" t="s" s="2">
         <v>664</v>
@@ -67890,7 +67888,7 @@
     </row>
     <row r="621" hidden="true">
       <c r="A621" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="B621" t="s" s="2">
         <v>666</v>
@@ -67994,7 +67992,7 @@
     </row>
     <row r="622" hidden="true">
       <c r="A622" t="s" s="2">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="B622" t="s" s="2">
         <v>668</v>
@@ -68098,7 +68096,7 @@
     </row>
     <row r="623" hidden="true">
       <c r="A623" t="s" s="2">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="B623" t="s" s="2">
         <v>670</v>
@@ -68202,7 +68200,7 @@
     </row>
     <row r="624" hidden="true">
       <c r="A624" t="s" s="2">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="B624" t="s" s="2">
         <v>650</v>
@@ -68218,7 +68216,7 @@
         <v>74</v>
       </c>
       <c r="G624" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H624" t="s" s="2">
         <v>73</v>
@@ -68306,7 +68304,7 @@
     </row>
     <row r="625" hidden="true">
       <c r="A625" t="s" s="2">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="B625" t="s" s="2">
         <v>656</v>
@@ -68406,7 +68404,7 @@
     </row>
     <row r="626" hidden="true">
       <c r="A626" t="s" s="2">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="B626" t="s" s="2">
         <v>658</v>
@@ -68508,7 +68506,7 @@
     </row>
     <row r="627" hidden="true">
       <c r="A627" t="s" s="2">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="B627" t="s" s="2">
         <v>660</v>
@@ -68612,7 +68610,7 @@
     </row>
     <row r="628" hidden="true">
       <c r="A628" t="s" s="2">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="B628" t="s" s="2">
         <v>664</v>
@@ -68714,7 +68712,7 @@
     </row>
     <row r="629" hidden="true">
       <c r="A629" t="s" s="2">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="B629" t="s" s="2">
         <v>666</v>
@@ -68818,7 +68816,7 @@
     </row>
     <row r="630" hidden="true">
       <c r="A630" t="s" s="2">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="B630" t="s" s="2">
         <v>668</v>
@@ -68922,7 +68920,7 @@
     </row>
     <row r="631" hidden="true">
       <c r="A631" t="s" s="2">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="B631" t="s" s="2">
         <v>670</v>
@@ -69026,7 +69024,7 @@
     </row>
     <row r="632" hidden="true">
       <c r="A632" t="s" s="2">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="B632" t="s" s="2">
         <v>650</v>
@@ -69042,7 +69040,7 @@
         <v>74</v>
       </c>
       <c r="G632" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H632" t="s" s="2">
         <v>73</v>
@@ -69130,7 +69128,7 @@
     </row>
     <row r="633" hidden="true">
       <c r="A633" t="s" s="2">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="B633" t="s" s="2">
         <v>656</v>
@@ -69230,7 +69228,7 @@
     </row>
     <row r="634" hidden="true">
       <c r="A634" t="s" s="2">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="B634" t="s" s="2">
         <v>658</v>
@@ -69332,7 +69330,7 @@
     </row>
     <row r="635" hidden="true">
       <c r="A635" t="s" s="2">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="B635" t="s" s="2">
         <v>660</v>
@@ -69436,7 +69434,7 @@
     </row>
     <row r="636" hidden="true">
       <c r="A636" t="s" s="2">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="B636" t="s" s="2">
         <v>664</v>
@@ -69538,7 +69536,7 @@
     </row>
     <row r="637" hidden="true">
       <c r="A637" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="B637" t="s" s="2">
         <v>666</v>
@@ -69642,7 +69640,7 @@
     </row>
     <row r="638" hidden="true">
       <c r="A638" t="s" s="2">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="B638" t="s" s="2">
         <v>668</v>
@@ -69746,7 +69744,7 @@
     </row>
     <row r="639" hidden="true">
       <c r="A639" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="B639" t="s" s="2">
         <v>670</v>
@@ -69850,7 +69848,7 @@
     </row>
     <row r="640" hidden="true">
       <c r="A640" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B640" t="s" s="2">
         <v>650</v>
@@ -69866,7 +69864,7 @@
         <v>74</v>
       </c>
       <c r="G640" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H640" t="s" s="2">
         <v>73</v>
@@ -69954,7 +69952,7 @@
     </row>
     <row r="641" hidden="true">
       <c r="A641" t="s" s="2">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="B641" t="s" s="2">
         <v>656</v>
@@ -70054,7 +70052,7 @@
     </row>
     <row r="642" hidden="true">
       <c r="A642" t="s" s="2">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="B642" t="s" s="2">
         <v>658</v>
@@ -70156,7 +70154,7 @@
     </row>
     <row r="643" hidden="true">
       <c r="A643" t="s" s="2">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="B643" t="s" s="2">
         <v>660</v>
@@ -70260,7 +70258,7 @@
     </row>
     <row r="644" hidden="true">
       <c r="A644" t="s" s="2">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="B644" t="s" s="2">
         <v>664</v>
@@ -70362,7 +70360,7 @@
     </row>
     <row r="645" hidden="true">
       <c r="A645" t="s" s="2">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="B645" t="s" s="2">
         <v>666</v>
@@ -70466,7 +70464,7 @@
     </row>
     <row r="646" hidden="true">
       <c r="A646" t="s" s="2">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="B646" t="s" s="2">
         <v>668</v>
@@ -70570,7 +70568,7 @@
     </row>
     <row r="647" hidden="true">
       <c r="A647" t="s" s="2">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="B647" t="s" s="2">
         <v>670</v>
@@ -70674,7 +70672,7 @@
     </row>
     <row r="648" hidden="true">
       <c r="A648" t="s" s="2">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="B648" t="s" s="2">
         <v>650</v>
@@ -70690,7 +70688,7 @@
         <v>74</v>
       </c>
       <c r="G648" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H648" t="s" s="2">
         <v>73</v>
@@ -70778,7 +70776,7 @@
     </row>
     <row r="649" hidden="true">
       <c r="A649" t="s" s="2">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="B649" t="s" s="2">
         <v>656</v>
@@ -70878,7 +70876,7 @@
     </row>
     <row r="650" hidden="true">
       <c r="A650" t="s" s="2">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="B650" t="s" s="2">
         <v>658</v>
@@ -70980,7 +70978,7 @@
     </row>
     <row r="651" hidden="true">
       <c r="A651" t="s" s="2">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="B651" t="s" s="2">
         <v>660</v>
@@ -71084,7 +71082,7 @@
     </row>
     <row r="652" hidden="true">
       <c r="A652" t="s" s="2">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="B652" t="s" s="2">
         <v>664</v>
@@ -71186,7 +71184,7 @@
     </row>
     <row r="653" hidden="true">
       <c r="A653" t="s" s="2">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="B653" t="s" s="2">
         <v>666</v>
@@ -71290,7 +71288,7 @@
     </row>
     <row r="654" hidden="true">
       <c r="A654" t="s" s="2">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="B654" t="s" s="2">
         <v>668</v>
@@ -71394,7 +71392,7 @@
     </row>
     <row r="655" hidden="true">
       <c r="A655" t="s" s="2">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="B655" t="s" s="2">
         <v>670</v>
@@ -71498,7 +71496,7 @@
     </row>
     <row r="656" hidden="true">
       <c r="A656" t="s" s="2">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="B656" t="s" s="2">
         <v>650</v>
@@ -71514,7 +71512,7 @@
         <v>74</v>
       </c>
       <c r="G656" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H656" t="s" s="2">
         <v>73</v>
@@ -71602,7 +71600,7 @@
     </row>
     <row r="657" hidden="true">
       <c r="A657" t="s" s="2">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="B657" t="s" s="2">
         <v>656</v>
@@ -71702,7 +71700,7 @@
     </row>
     <row r="658" hidden="true">
       <c r="A658" t="s" s="2">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="B658" t="s" s="2">
         <v>658</v>
@@ -71804,7 +71802,7 @@
     </row>
     <row r="659" hidden="true">
       <c r="A659" t="s" s="2">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="B659" t="s" s="2">
         <v>660</v>
@@ -71908,7 +71906,7 @@
     </row>
     <row r="660" hidden="true">
       <c r="A660" t="s" s="2">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="B660" t="s" s="2">
         <v>664</v>
@@ -72010,7 +72008,7 @@
     </row>
     <row r="661" hidden="true">
       <c r="A661" t="s" s="2">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="B661" t="s" s="2">
         <v>666</v>
@@ -72114,7 +72112,7 @@
     </row>
     <row r="662" hidden="true">
       <c r="A662" t="s" s="2">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="B662" t="s" s="2">
         <v>668</v>
@@ -72218,7 +72216,7 @@
     </row>
     <row r="663" hidden="true">
       <c r="A663" t="s" s="2">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="B663" t="s" s="2">
         <v>670</v>
@@ -72322,7 +72320,7 @@
     </row>
     <row r="664" hidden="true">
       <c r="A664" t="s" s="2">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="B664" t="s" s="2">
         <v>650</v>
@@ -72338,7 +72336,7 @@
         <v>74</v>
       </c>
       <c r="G664" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H664" t="s" s="2">
         <v>73</v>
@@ -72426,7 +72424,7 @@
     </row>
     <row r="665" hidden="true">
       <c r="A665" t="s" s="2">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="B665" t="s" s="2">
         <v>656</v>
@@ -72526,7 +72524,7 @@
     </row>
     <row r="666" hidden="true">
       <c r="A666" t="s" s="2">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="B666" t="s" s="2">
         <v>658</v>
@@ -72628,7 +72626,7 @@
     </row>
     <row r="667" hidden="true">
       <c r="A667" t="s" s="2">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="B667" t="s" s="2">
         <v>660</v>
@@ -72732,7 +72730,7 @@
     </row>
     <row r="668" hidden="true">
       <c r="A668" t="s" s="2">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="B668" t="s" s="2">
         <v>664</v>
@@ -72834,7 +72832,7 @@
     </row>
     <row r="669" hidden="true">
       <c r="A669" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B669" t="s" s="2">
         <v>666</v>
@@ -72938,7 +72936,7 @@
     </row>
     <row r="670" hidden="true">
       <c r="A670" t="s" s="2">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="B670" t="s" s="2">
         <v>668</v>
@@ -73042,7 +73040,7 @@
     </row>
     <row r="671" hidden="true">
       <c r="A671" t="s" s="2">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="B671" t="s" s="2">
         <v>670</v>
@@ -73146,7 +73144,7 @@
     </row>
     <row r="672" hidden="true">
       <c r="A672" t="s" s="2">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="B672" t="s" s="2">
         <v>650</v>
@@ -73162,7 +73160,7 @@
         <v>74</v>
       </c>
       <c r="G672" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H672" t="s" s="2">
         <v>73</v>
@@ -73250,7 +73248,7 @@
     </row>
     <row r="673" hidden="true">
       <c r="A673" t="s" s="2">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="B673" t="s" s="2">
         <v>656</v>
@@ -73350,7 +73348,7 @@
     </row>
     <row r="674" hidden="true">
       <c r="A674" t="s" s="2">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="B674" t="s" s="2">
         <v>658</v>
@@ -73452,7 +73450,7 @@
     </row>
     <row r="675" hidden="true">
       <c r="A675" t="s" s="2">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="B675" t="s" s="2">
         <v>660</v>
@@ -73556,7 +73554,7 @@
     </row>
     <row r="676" hidden="true">
       <c r="A676" t="s" s="2">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="B676" t="s" s="2">
         <v>664</v>
@@ -73658,7 +73656,7 @@
     </row>
     <row r="677" hidden="true">
       <c r="A677" t="s" s="2">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="B677" t="s" s="2">
         <v>666</v>
@@ -73762,7 +73760,7 @@
     </row>
     <row r="678" hidden="true">
       <c r="A678" t="s" s="2">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="B678" t="s" s="2">
         <v>668</v>
@@ -73866,7 +73864,7 @@
     </row>
     <row r="679" hidden="true">
       <c r="A679" t="s" s="2">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="B679" t="s" s="2">
         <v>670</v>
@@ -73970,7 +73968,7 @@
     </row>
     <row r="680" hidden="true">
       <c r="A680" t="s" s="2">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="B680" t="s" s="2">
         <v>650</v>
@@ -73986,7 +73984,7 @@
         <v>74</v>
       </c>
       <c r="G680" t="s" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H680" t="s" s="2">
         <v>73</v>
@@ -74074,7 +74072,7 @@
     </row>
     <row r="681" hidden="true">
       <c r="A681" t="s" s="2">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="B681" t="s" s="2">
         <v>656</v>
@@ -74174,7 +74172,7 @@
     </row>
     <row r="682" hidden="true">
       <c r="A682" t="s" s="2">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="B682" t="s" s="2">
         <v>658</v>
@@ -74276,7 +74274,7 @@
     </row>
     <row r="683" hidden="true">
       <c r="A683" t="s" s="2">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="B683" t="s" s="2">
         <v>660</v>
@@ -74380,7 +74378,7 @@
     </row>
     <row r="684" hidden="true">
       <c r="A684" t="s" s="2">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="B684" t="s" s="2">
         <v>664</v>
@@ -74482,7 +74480,7 @@
     </row>
     <row r="685" hidden="true">
       <c r="A685" t="s" s="2">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="B685" t="s" s="2">
         <v>666</v>
@@ -74586,7 +74584,7 @@
     </row>
     <row r="686" hidden="true">
       <c r="A686" t="s" s="2">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="B686" t="s" s="2">
         <v>668</v>
@@ -74690,7 +74688,7 @@
     </row>
     <row r="687" hidden="true">
       <c r="A687" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="B687" t="s" s="2">
         <v>670</v>
@@ -74794,13 +74792,13 @@
     </row>
     <row r="688" hidden="true">
       <c r="A688" t="s" s="2">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="B688" t="s" s="2">
         <v>650</v>
       </c>
       <c r="C688" t="s" s="2">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="D688" t="s" s="2">
         <v>73</v>
@@ -74825,7 +74823,7 @@
         <v>140</v>
       </c>
       <c r="L688" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="M688" t="s" s="2">
         <v>335</v>
@@ -74863,7 +74861,7 @@
       </c>
       <c r="Y688" s="2"/>
       <c r="Z688" t="s" s="2">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="AA688" t="s" s="2">
         <v>73</v>
@@ -74898,13 +74896,13 @@
     </row>
     <row r="689" hidden="true">
       <c r="A689" t="s" s="2">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="B689" t="s" s="2">
         <v>650</v>
       </c>
       <c r="C689" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D689" t="s" s="2">
         <v>73</v>
@@ -74929,7 +74927,7 @@
         <v>140</v>
       </c>
       <c r="L689" t="s" s="2">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="M689" t="s" s="2">
         <v>335</v>
@@ -74967,7 +74965,7 @@
       </c>
       <c r="Y689" s="2"/>
       <c r="Z689" t="s" s="2">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="AA689" t="s" s="2">
         <v>73</v>
@@ -75002,7 +75000,7 @@
     </row>
     <row r="690" hidden="true">
       <c r="A690" t="s" s="2">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="B690" t="s" s="2">
         <v>814</v>
@@ -75106,7 +75104,7 @@
     </row>
     <row r="691" hidden="true">
       <c r="A691" t="s" s="2">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="B691" t="s" s="2">
         <v>815</v>
@@ -75210,7 +75208,7 @@
     </row>
     <row r="692" hidden="true">
       <c r="A692" t="s" s="2">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="B692" t="s" s="2">
         <v>819</v>
@@ -75312,10 +75310,10 @@
     </row>
     <row r="693" hidden="true">
       <c r="A693" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="B693" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="C693" s="2"/>
       <c r="D693" t="s" s="2">
@@ -75338,19 +75336,19 @@
         <v>73</v>
       </c>
       <c r="K693" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="L693" t="s" s="2">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="M693" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="N693" t="s" s="2">
         <v>645</v>
       </c>
       <c r="O693" t="s" s="2">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="P693" t="s" s="2">
         <v>73</v>
@@ -75379,7 +75377,7 @@
       </c>
       <c r="Y693" s="2"/>
       <c r="Z693" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="AA693" t="s" s="2">
         <v>73</v>
@@ -75397,7 +75395,7 @@
         <v>73</v>
       </c>
       <c r="AF693" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="AG693" t="s" s="2">
         <v>74</v>

--- a/ig/nr-corrections/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/nr-corrections/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:26:19+00:00</t>
+    <t>2024-02-12T14:49:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/nr-corrections/StructureDefinition-as-dr-practitioner.xlsx
+++ b/ig/nr-corrections/StructureDefinition-as-dr-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-02-12T14:49:01+00:00</t>
+    <t>2024-02-16T11:05:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1033,7 +1033,8 @@
 </t>
   </si>
   <si>
-    <t>Description of identifier</t>
+    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
+Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
   </si>
   <si>
     <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
@@ -1299,8 +1300,7 @@
     <t>Practitioner.identifier:idNatPs.type</t>
   </si>
   <si>
-    <t>Type d’identifiant national de la personne physique (typeIdNat_PP),
-Les codes ADELI, RPPS et IDNPS proviennent du system  http://interopsante.org/fhir/CodeSystem/fr-v2-0203 ; Les codes 1, 3, 4, 5, 6 proviennent du system : https://mos.esante.gouv.fr/NOS/TRE_G08-TypeIdentifiantPersonne/FHIR/TRE-G08-TypeIdentifiantPersonne</t>
+    <t>Description of identifier</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;
@@ -3031,7 +3031,7 @@
     <t>exercicePro</t>
   </si>
   <si>
-    <t>profession : exercice professionnel ou future profession de l'étudiant et la catégorie de profession.</t>
+    <t>exercicePro : exercice professionnel décrivant la profession exercée, l'identité d'exercice d'un professionnel et le cadre de son exercice (civil, militaire, etc.).</t>
   </si>
   <si>
     <t>Practitioner.qualification:exercicePro.id</t>
@@ -15455,7 +15455,7 @@
         <v>323</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>324</v>
+        <v>410</v>
       </c>
       <c r="M111" t="s" s="2">
         <v>325</v>
@@ -17509,7 +17509,7 @@
         <v>323</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>324</v>
+        <v>410</v>
       </c>
       <c r="M131" t="s" s="2">
         <v>325</v>
@@ -19244,7 +19244,7 @@
         <v>74</v>
       </c>
       <c r="G148" t="s" s="2">
-        <v>75</v>
+        <v>81</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>82</v>
@@ -20168,7 +20168,7 @@
         <v>74</v>
       </c>
       <c r="G157" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H157" t="s" s="2">
         <v>82</v>
@@ -22634,7 +22634,7 @@
         <v>74</v>
       </c>
       <c r="G181" t="s" s="2">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H181" t="s" s="2">
         <v>73</v>
